--- a/test-cases/test-case.xlsx
+++ b/test-cases/test-case.xlsx
@@ -901,10 +901,10 @@
         <v>59</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>28</v>
@@ -921,10 +921,10 @@
         <v>59</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>28</v>
